--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -1,31 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C89DADF-1CE2-4049-B802-725A44940926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751A38E9-33A7-4E82-83A7-282AFA983D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="2" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" firstSheet="4" activeTab="11" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
     <sheet name="ItemDataTable_Meta" sheetId="7" r:id="rId2"/>
-    <sheet name="LocalizationTable" sheetId="15" r:id="rId3"/>
-    <sheet name="KeycodeDataTable" sheetId="13" r:id="rId4"/>
-    <sheet name="ProductDataTable" sheetId="3" r:id="rId5"/>
-    <sheet name="Calculator" sheetId="14" r:id="rId6"/>
-    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId7"/>
-    <sheet name="EventDataTable" sheetId="4" r:id="rId8"/>
-    <sheet name="ObjectDataTable" sheetId="5" r:id="rId9"/>
-    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId10"/>
+    <sheet name="ProductDataTable" sheetId="3" r:id="rId3"/>
+    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId4"/>
+    <sheet name="ObjectDataTable" sheetId="5" r:id="rId5"/>
+    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId6"/>
+    <sheet name="EventDataTable" sheetId="4" r:id="rId7"/>
+    <sheet name="KeycodeDataTable" sheetId="13" r:id="rId8"/>
+    <sheet name="LocalizationTable" sheetId="15" r:id="rId9"/>
+    <sheet name="Calculator" sheetId="14" r:id="rId10"/>
     <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId11"/>
+    <sheet name="ConfigDataTable" sheetId="18" r:id="rId12"/>
+    <sheet name="ConfigDataTable_Edit" sheetId="16" r:id="rId13"/>
+    <sheet name="ConfigDataTable_Meta" sheetId="17" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -65,13 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="398">
-  <si>
-    <t>ItemID</t>
-  </si>
-  <si>
-    <t>ItemName</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="492">
   <si>
     <t>PriceStdDev</t>
   </si>
@@ -79,9 +77,6 @@
     <t>GrowthTime</t>
   </si>
   <si>
-    <t>WaterConsumption</t>
-  </si>
-  <si>
     <t>Potato</t>
   </si>
   <si>
@@ -106,10 +101,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Seed</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -131,18 +122,6 @@
   </si>
   <si>
     <t>StoragePeriod</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EventID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EventType</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -353,10 +332,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>BasicPrice</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Type</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -513,22 +488,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>ObjectID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Cow</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>ObjectName</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>ObjectType</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Cattle</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -539,10 +502,6 @@
   <si>
     <t>NPC</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Price</t>
-    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Chicken</t>
@@ -553,10 +512,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>ProductionAmount</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>오브젝트 일련번호</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -593,17 +548,9 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>데모버전 사용 여부</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>TargetUI</t>
   </si>
   <si>
-    <t>ActionType</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>IsRebindable</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -632,10 +579,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>S</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>PopUp_Shop</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -684,26 +627,14 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Chicken</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Object</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>KeyID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DefaultKeyCode</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Movement</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>UI</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -757,10 +688,6 @@
   </si>
   <si>
     <t>3번 슬롯</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionName</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -2066,10 +1993,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Korean</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2191,6 +2114,466 @@
   </si>
   <si>
     <t>축사</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DailyYield</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>YieldCoolDown</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sheep</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>YieldMaterial</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>YieldItem</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxCapacity</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>W</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Movement</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC_MoveLeft</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC_MoveRight</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>위로 이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>왼쪽으로 이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아래로 이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC_MoveUp</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC_MoveDown</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽으로 이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>M</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RealTimePerDay</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RocketSlotAmount</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RocketDeliveryTime</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RocketLoadingTime</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GraceInterest</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MarketOpenHour</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MarketCloseHour</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동 마다 사용되는 베터리 용량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 기준 1년</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 기준 1달</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로켓 용량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventProb</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RumorProb</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RumorStdMul</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FollowUpDecay</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FollowUpOverMeanMul</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>유예 기간 이자 비율</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로켓 이동 시간(초 단위)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로켓 상하차 시간(초 단위)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 오버 유예 기간(게임 내 일 단위)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>장 마감 시간(게임 내 시간 단위)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임 내 하루의 실제 시간(초 단위)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트 발생 확률</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>소문 발생 확률</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>소문 적용 시 표준편차 변동 비율</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>후속 이벤트 발생 확률(0.7^연속 일수)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>목표 미달 시 반전될 확률</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴급 이벤트 발생 확률</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴급 이벤트 최소 진행 기간</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴급 이벤트 최대 진행 기간</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴급 이벤트 재 발생 쿨 타임</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgProb</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgMinDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgMaxDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgAfterLockReachDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgAfterLockExpireDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgLockDecay</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴급 이벤트 목표 달성 종료 시,  평균 회귀 유예 최소 기간</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴급 이벤트 기간 만료 종료 시, 평균 회귀 유예 최소 기간</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>유예 최소 기간 이후 유예 유지 확률 (0.7 ^ 연속 일수)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UsedBatteryPerWork</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DaysPerYear</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DaysPerMonth</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgVirtualLineMul</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>긴급 이벤트 가상 선 강도 (기존 지지/저항 선의 0.3배)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgVirtualLineKeepDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>가상선 유지 기간</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegressionRangeMin</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>RegressionRangeMax</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LineSampleDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LineSettleDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LineBinSigma</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지지/저항선 표본</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지지/저항선 형성 주기</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LineMinSamples</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>선이 형성되기 위한 최소한의 표본 개수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LineBlockDecay</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>LineQuietPower</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지지/저항선이 한 번 부딪힐 때 줄어드는 강도 비율</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaxPeriodDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EndingGoalMoney</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartingPotatoSeed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartingPotato</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartingNPC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartingMoney</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>세금 지출 주기</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>굿 엔딩 기준 금액</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작 지원 아이템 : 씨 감자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작 지원 아이템 : 감자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작 지원 아이템 : 기본 NPC 로봇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작 지원 아이템 : 정착 지원금</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EmgCoolDownDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BadEndGraceDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균회귀 목표 예외 범위(0.5~2배를 벗어난 경우엔 원가를 목표로)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>28일 표본 중, 비슷한 가격대 끼리 묶는 배수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>장 시작 시간(게임 내 시간 단위)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이벤트가 없는 날의 고정 돌파 강도</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpireWarningDays</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeScaleMax</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeScaleStep</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>유통기한 경고 일수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간 배수 증가 배율 (0.5씩 증가)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 시간 배수 증가 수치</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UITimeStepMinutes</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldMaxExpand</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI 시간 표시 최소 단위(10분단위)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 방향 별 필드 확장 최대 횟수</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2198,6 +2581,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
+  </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2412,7 +2798,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2625,6 +3011,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2888,7 +3286,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2936,6 +3334,18 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2989,41 +3399,6 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3084,6 +3459,41 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3480,54 +3890,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6335F4D-6333-4BEC-B869-C3B1C6B3F47D}">
-  <dimension ref="A1:L38"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="2" customWidth="1"/>
-    <col min="8" max="9" width="13.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11.625" style="2" customWidth="1"/>
     <col min="11" max="11" width="11.875" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.5" style="2" customWidth="1"/>
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1011</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2">
         <f>D3*90/100</f>
@@ -3537,21 +3952,24 @@
         <v>45</v>
       </c>
       <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
         <v>-1</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1012</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2">
         <v>1000</v>
@@ -3560,21 +3978,24 @@
         <v>9</v>
       </c>
       <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
         <v>30</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1021</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2">
         <v>800</v>
@@ -3583,21 +4004,24 @@
         <v>45</v>
       </c>
       <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
         <v>-1</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2">
         <v>900</v>
@@ -3606,21 +4030,24 @@
         <v>9</v>
       </c>
       <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
         <v>30</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2011</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2">
         <f>D7*90/100</f>
@@ -3630,21 +4057,24 @@
         <v>45</v>
       </c>
       <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
         <v>-1</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2012</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2">
         <v>1000</v>
@@ -3653,21 +4083,24 @@
         <v>9</v>
       </c>
       <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
         <v>20</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2">
         <f>D9*90/100</f>
@@ -3677,21 +4110,24 @@
         <v>45</v>
       </c>
       <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
         <v>-1</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D9" s="2">
         <v>1100</v>
@@ -3700,21 +4136,24 @@
         <v>9</v>
       </c>
       <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
         <v>20</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>3011</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2">
         <v>1100</v>
@@ -3723,21 +4162,24 @@
         <v>45</v>
       </c>
       <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
         <v>-1</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>3012</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2">
         <v>1200</v>
@@ -3746,21 +4188,24 @@
         <v>9</v>
       </c>
       <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
         <v>15</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>3021</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2">
         <f>D13*90/100</f>
@@ -3770,21 +4215,24 @@
         <v>45</v>
       </c>
       <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
         <v>-1</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>3022</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2">
         <v>1100</v>
@@ -3793,21 +4241,24 @@
         <v>9</v>
       </c>
       <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
         <v>15</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>4011</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2">
         <v>5000</v>
@@ -3816,21 +4267,24 @@
         <v>8</v>
       </c>
       <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
         <v>-1</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>4012</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2">
         <v>5000</v>
@@ -3839,21 +4293,24 @@
         <v>4</v>
       </c>
       <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
         <v>7</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>5001</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -3862,21 +4319,24 @@
         <v>99</v>
       </c>
       <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
         <v>-1</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>5011</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -3885,21 +4345,24 @@
         <v>1</v>
       </c>
       <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
         <v>-1</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>5021</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -3908,21 +4371,24 @@
         <v>1</v>
       </c>
       <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
         <v>-1</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>6021</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D19" s="2">
         <v>10000</v>
@@ -3931,21 +4397,24 @@
         <v>1</v>
       </c>
       <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
         <v>-1</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>6031</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D20" s="2">
         <v>20000</v>
@@ -3954,21 +4423,24 @@
         <v>1</v>
       </c>
       <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
         <v>-1</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>6032</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>379</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D21" s="2">
         <v>5000</v>
@@ -3977,21 +4449,24 @@
         <v>1</v>
       </c>
       <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
         <v>-1</v>
       </c>
-      <c r="G21" s="2">
+      <c r="H21" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>7011</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D22" s="2">
         <v>1000</v>
@@ -4000,21 +4475,24 @@
         <v>1</v>
       </c>
       <c r="F22" s="2">
+        <v>300</v>
+      </c>
+      <c r="G22" s="2">
         <v>-1</v>
       </c>
-      <c r="G22" s="2">
+      <c r="H22" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>8011</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D23" s="2">
         <v>10000</v>
@@ -4023,21 +4501,24 @@
         <v>1</v>
       </c>
       <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
         <v>-1</v>
       </c>
-      <c r="G23" s="2">
+      <c r="H23" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>8012</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D24" s="2">
         <v>20000</v>
@@ -4046,21 +4527,24 @@
         <v>1</v>
       </c>
       <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
         <v>-1</v>
       </c>
-      <c r="G24" s="2">
+      <c r="H24" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>8021</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D25" s="2">
         <v>10000</v>
@@ -4069,21 +4553,24 @@
         <v>1</v>
       </c>
       <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
         <v>-1</v>
       </c>
-      <c r="G25" s="2">
+      <c r="H25" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>8022</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D26" s="2">
         <v>20000</v>
@@ -4092,21 +4579,24 @@
         <v>1</v>
       </c>
       <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2">
         <v>-1</v>
       </c>
-      <c r="G26" s="2">
+      <c r="H26" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>8031</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D27" s="2">
         <v>10000</v>
@@ -4115,21 +4605,24 @@
         <v>1</v>
       </c>
       <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
         <v>-1</v>
       </c>
-      <c r="G27" s="2">
+      <c r="H27" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>8032</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D28" s="2">
         <v>20000</v>
@@ -4138,21 +4631,24 @@
         <v>1</v>
       </c>
       <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
         <v>-1</v>
       </c>
-      <c r="G28" s="2">
+      <c r="H28" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>8041</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D29" s="2">
         <v>10000</v>
@@ -4161,21 +4657,24 @@
         <v>1</v>
       </c>
       <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
         <v>-1</v>
       </c>
-      <c r="G29" s="2">
+      <c r="H29" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>8042</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D30" s="2">
         <v>20000</v>
@@ -4184,21 +4683,24 @@
         <v>1</v>
       </c>
       <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
         <v>-1</v>
       </c>
-      <c r="G30" s="2">
+      <c r="H30" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>9001</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -4207,21 +4709,24 @@
         <v>1</v>
       </c>
       <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
         <v>-1</v>
       </c>
-      <c r="G31" s="2">
+      <c r="H31" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>9011</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D32" s="2">
         <v>100000</v>
@@ -4230,21 +4735,24 @@
         <v>1</v>
       </c>
       <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
         <v>-1</v>
       </c>
-      <c r="G32" s="2">
+      <c r="H32" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>9021</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D33" s="2">
         <v>30000</v>
@@ -4253,15 +4761,13 @@
         <v>1</v>
       </c>
       <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
         <v>-1</v>
       </c>
-      <c r="G33" s="2">
+      <c r="H33" s="2">
         <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L38" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -4304,137 +4810,101 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67515829-0AFB-4F47-8C6E-31EBDF1B0551}">
+  <sheetPr codeName="Sheet10"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A11">TRANSPOSE(ObjectDataTable!A1:J1)</f>
-        <v>ObjectID</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <v>ObjectName</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="str">
-        <v>ObjectType</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="str">
-        <v>Price</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="str">
-        <v>MainInv</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <v>SubInv</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
-        <v>Speed</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <v>WorkDuration</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <v>ProductionAmount</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="str">
-        <v>UseToDemo</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>4012</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Milk</v>
+      </c>
+      <c r="C4" s="2">
+        <f>VLOOKUP(A4-1, ItemDataTable!A:D, 4, FALSE)</f>
+        <v>5000</v>
+      </c>
+      <c r="D4" s="2">
+        <f>VLOOKUP(A4, ProductDataTable!A:E,5, FALSE)</f>
+        <v>-1</v>
+      </c>
+      <c r="E4" s="2">
+        <f>VLOOKUP(A4, ProductDataTable!A:E,4, FALSE)</f>
+        <v>0.2</v>
+      </c>
+      <c r="F4" s="11">
+        <f>D4*(1-(E4*2))</f>
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="2">
+        <f>1000/100*90</f>
+        <v>900</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="F6" s="12">
+        <f>D6*(1-(E6*2))</f>
+        <v>880</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F2"/>
+  </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4442,6 +4912,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F110"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4456,22 +4927,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4479,13 +4950,13 @@
         <v>100001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
@@ -4495,13 +4966,13 @@
         <v>100002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -4511,13 +4982,13 @@
         <v>100003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4527,13 +4998,13 @@
         <v>110001</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -4543,17 +5014,17 @@
         <v>110002</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="7" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4561,13 +5032,13 @@
         <v>110003</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -4577,13 +5048,13 @@
         <v>110004</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -4593,13 +5064,13 @@
         <v>110005</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -4609,13 +5080,13 @@
         <v>110006</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
@@ -4625,13 +5096,13 @@
         <v>110007</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
@@ -4641,17 +5112,17 @@
         <v>110008</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="7" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4659,13 +5130,13 @@
         <v>110009</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -4675,13 +5146,13 @@
         <v>110010</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -4691,17 +5162,17 @@
         <v>110011</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="7" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4709,13 +5180,13 @@
         <v>110012</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -4725,13 +5196,13 @@
         <v>110013</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -4741,13 +5212,13 @@
         <v>110014</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>189</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -4757,17 +5228,17 @@
         <v>110015</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="7" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4775,17 +5246,17 @@
         <v>110016</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="7" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4793,17 +5264,17 @@
         <v>110017</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="7" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4811,13 +5282,13 @@
         <v>110018</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -4827,13 +5298,13 @@
         <v>110019</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -4843,17 +5314,17 @@
         <v>110020</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="7" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4861,13 +5332,13 @@
         <v>110021</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -4877,13 +5348,13 @@
         <v>110022</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -4893,17 +5364,17 @@
         <v>110023</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="7" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4911,17 +5382,17 @@
         <v>110024</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="7" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4929,13 +5400,13 @@
         <v>110025</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -4945,13 +5416,13 @@
         <v>110026</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -4961,13 +5432,13 @@
         <v>110027</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -4977,17 +5448,17 @@
         <v>110028</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="7" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4995,17 +5466,17 @@
         <v>110029</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="7" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5013,17 +5484,17 @@
         <v>110030</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="7" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5031,17 +5502,17 @@
         <v>110031</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="7" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5049,17 +5520,17 @@
         <v>110032</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="E36" s="8"/>
       <c r="F36" s="7" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5067,13 +5538,13 @@
         <v>110033</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="7"/>
@@ -5083,13 +5554,13 @@
         <v>110034</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="8"/>
@@ -5099,13 +5570,13 @@
         <v>110035</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -5115,13 +5586,13 @@
         <v>110036</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -5131,13 +5602,13 @@
         <v>110037</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -5147,17 +5618,17 @@
         <v>110038</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="7" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5165,17 +5636,17 @@
         <v>110039</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="7" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5183,13 +5654,13 @@
         <v>110040</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -5199,17 +5670,17 @@
         <v>110041</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="7" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5217,13 +5688,13 @@
         <v>110042</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -5233,17 +5704,17 @@
         <v>110043</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="E47" s="8"/>
       <c r="F47" s="7" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5251,17 +5722,17 @@
         <v>110044</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="7" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5269,17 +5740,17 @@
         <v>110045</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="E49" s="8"/>
       <c r="F49" s="7" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5287,13 +5758,13 @@
         <v>110046</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
@@ -5303,17 +5774,17 @@
         <v>110047</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="7" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5321,13 +5792,13 @@
         <v>110048</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
@@ -5337,17 +5808,17 @@
         <v>110049</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="7" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5355,17 +5826,17 @@
         <v>110050</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="7" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5373,13 +5844,13 @@
         <v>110051</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
@@ -5389,17 +5860,17 @@
         <v>110052</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="7" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5407,13 +5878,13 @@
         <v>110053</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -5423,13 +5894,13 @@
         <v>110054</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
@@ -5439,13 +5910,13 @@
         <v>110055</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
@@ -5455,13 +5926,13 @@
         <v>110056</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
@@ -5471,17 +5942,17 @@
         <v>110057</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="7" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5489,13 +5960,13 @@
         <v>110058</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
@@ -5505,13 +5976,13 @@
         <v>110059</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
@@ -5521,13 +5992,13 @@
         <v>110060</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
@@ -5537,17 +6008,17 @@
         <v>110061</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="7" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5555,13 +6026,13 @@
         <v>110062</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
@@ -5571,13 +6042,13 @@
         <v>110063</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
@@ -5587,17 +6058,17 @@
         <v>110064</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="7" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5605,17 +6076,17 @@
         <v>110065</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="7" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5623,17 +6094,17 @@
         <v>110066</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="7" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5641,17 +6112,17 @@
         <v>110067</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="E71" s="8"/>
       <c r="F71" s="7" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5659,17 +6130,17 @@
         <v>110068</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="E72" s="8"/>
       <c r="F72" s="7" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5677,17 +6148,17 @@
         <v>110069</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="7" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5695,13 +6166,13 @@
         <v>110070</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
@@ -5711,17 +6182,17 @@
         <v>110071</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="7" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5729,13 +6200,13 @@
         <v>110072</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -5745,13 +6216,13 @@
         <v>110073</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -5761,13 +6232,13 @@
         <v>110074</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
@@ -5777,13 +6248,13 @@
         <v>110075</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
@@ -5793,17 +6264,17 @@
         <v>110076</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="E80" s="8"/>
       <c r="F80" s="7" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5811,13 +6282,13 @@
         <v>110077</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
@@ -5827,13 +6298,13 @@
         <v>110078</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
@@ -5843,17 +6314,17 @@
         <v>110079</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="E83" s="8"/>
       <c r="F83" s="7" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5861,17 +6332,17 @@
         <v>110080</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="7" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5879,13 +6350,13 @@
         <v>110081</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
@@ -5895,17 +6366,17 @@
         <v>110082</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="E86" s="8"/>
       <c r="F86" s="7" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5913,13 +6384,13 @@
         <v>110083</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
@@ -5929,17 +6400,17 @@
         <v>110084</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="9" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5947,13 +6418,13 @@
         <v>110085</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
@@ -5963,13 +6434,13 @@
         <v>110086</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
@@ -5979,13 +6450,13 @@
         <v>110087</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
@@ -5995,13 +6466,13 @@
         <v>110088</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
@@ -6011,17 +6482,17 @@
         <v>110089</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="E93" s="8"/>
       <c r="F93" s="7" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6029,17 +6500,17 @@
         <v>110090</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E94" s="8"/>
       <c r="F94" s="7" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6047,13 +6518,13 @@
         <v>110091</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
@@ -6063,13 +6534,13 @@
         <v>110092</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
@@ -6079,17 +6550,17 @@
         <v>110093</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="E97" s="8"/>
       <c r="F97" s="7" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6097,17 +6568,17 @@
         <v>110094</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="7" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6115,17 +6586,17 @@
         <v>110095</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="E99" s="8"/>
       <c r="F99" s="7" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6133,13 +6604,13 @@
         <v>110096</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
@@ -6149,13 +6620,13 @@
         <v>110097</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
@@ -6165,17 +6636,17 @@
         <v>110098</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="E102" s="8"/>
       <c r="F102" s="7" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6183,13 +6654,13 @@
         <v>110099</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
@@ -6199,13 +6670,13 @@
         <v>110100</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
@@ -6215,17 +6686,17 @@
         <v>110101</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="E105" s="8"/>
       <c r="F105" s="7" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6233,13 +6704,13 @@
         <v>110102</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
@@ -6249,13 +6720,13 @@
         <v>190001</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
@@ -6265,17 +6736,17 @@
         <v>190002</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="E108" s="8"/>
       <c r="F108" s="7" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6283,13 +6754,13 @@
         <v>190101</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
@@ -6299,13 +6770,13 @@
         <v>190102</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
@@ -6320,9 +6791,1244 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F807C416-FB0B-451D-B155-C2F36043718F}">
+  <dimension ref="A1:AR2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="23.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="24" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16" style="2" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="str" cm="1">
+        <f t="array" ref="A1:AR2">TRANSPOSE(_xlfn.DROP(_xlfn._xlws.FILTER(ConfigDataTable_Edit!A:B, ConfigDataTable_Edit!A:A&lt;&gt;""), 1))</f>
+        <v>UsedBatteryPerWork</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>RealTimePerDay</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>DaysPerYear</v>
+      </c>
+      <c r="D1" s="2" t="str">
+        <v>DaysPerMonth</v>
+      </c>
+      <c r="E1" s="2" t="str">
+        <v>RocketSlotAmount</v>
+      </c>
+      <c r="F1" s="2" t="str">
+        <v>RocketDeliveryTime</v>
+      </c>
+      <c r="G1" s="2" t="str">
+        <v>RocketLoadingTime</v>
+      </c>
+      <c r="H1" s="2" t="str">
+        <v>BadEndGraceDays</v>
+      </c>
+      <c r="I1" s="2" t="str">
+        <v>GraceInterest</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <v>MarketOpenHour</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <v>MarketCloseHour</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <v>EventProb</v>
+      </c>
+      <c r="M1" s="2" t="str">
+        <v>RumorProb</v>
+      </c>
+      <c r="N1" s="2" t="str">
+        <v>RumorStdMul</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <v>FollowUpDecay</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <v>FollowUpOverMeanMul</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>EmgProb</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>EmgMinDays</v>
+      </c>
+      <c r="S1" s="2" t="str">
+        <v>EmgMaxDays</v>
+      </c>
+      <c r="T1" s="2" t="str">
+        <v>EmgCoolDownDays</v>
+      </c>
+      <c r="U1" s="2" t="str">
+        <v>EmgAfterLockReachDays</v>
+      </c>
+      <c r="V1" s="2" t="str">
+        <v>EmgAfterLockExpireDays</v>
+      </c>
+      <c r="W1" s="2" t="str">
+        <v>EmgLockDecay</v>
+      </c>
+      <c r="X1" s="2" t="str">
+        <v>EmgVirtualLineMul</v>
+      </c>
+      <c r="Y1" s="2" t="str">
+        <v>EmgVirtualLineKeepDays</v>
+      </c>
+      <c r="Z1" s="2" t="str">
+        <v>RegressionRangeMin</v>
+      </c>
+      <c r="AA1" s="2" t="str">
+        <v>RegressionRangeMax</v>
+      </c>
+      <c r="AB1" s="2" t="str">
+        <v>LineSampleDays</v>
+      </c>
+      <c r="AC1" s="2" t="str">
+        <v>LineSettleDays</v>
+      </c>
+      <c r="AD1" s="2" t="str">
+        <v>LineBinSigma</v>
+      </c>
+      <c r="AE1" s="2" t="str">
+        <v>LineMinSamples</v>
+      </c>
+      <c r="AF1" s="2" t="str">
+        <v>LineBlockDecay</v>
+      </c>
+      <c r="AG1" s="2" t="str">
+        <v>LineQuietPower</v>
+      </c>
+      <c r="AH1" s="2" t="str">
+        <v>TaxPeriodDays</v>
+      </c>
+      <c r="AI1" s="2" t="str">
+        <v>EndingGoalMoney</v>
+      </c>
+      <c r="AJ1" s="2" t="str">
+        <v>StartingPotatoSeed</v>
+      </c>
+      <c r="AK1" s="2" t="str">
+        <v>StartingPotato</v>
+      </c>
+      <c r="AL1" s="2" t="str">
+        <v>StartingNPC</v>
+      </c>
+      <c r="AM1" s="2" t="str">
+        <v>StartingMoney</v>
+      </c>
+      <c r="AN1" s="2" t="str">
+        <v>ExpireWarningDays</v>
+      </c>
+      <c r="AO1" s="2" t="str">
+        <v>TimeScaleStep</v>
+      </c>
+      <c r="AP1" s="2" t="str">
+        <v>TimeScaleMax</v>
+      </c>
+      <c r="AQ1" s="2" t="str">
+        <v>UITimeStepMinutes</v>
+      </c>
+      <c r="AR1" s="2" t="str">
+        <v>FieldMaxExpand</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>600</v>
+      </c>
+      <c r="C2" s="2">
+        <v>336</v>
+      </c>
+      <c r="D2" s="2">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2">
+        <v>7200</v>
+      </c>
+      <c r="G2" s="2">
+        <v>7200</v>
+      </c>
+      <c r="H2" s="2">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>9</v>
+      </c>
+      <c r="K2" s="2">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="O2" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="P2" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="R2" s="2">
+        <v>7</v>
+      </c>
+      <c r="S2" s="2">
+        <v>14</v>
+      </c>
+      <c r="T2" s="2">
+        <v>28</v>
+      </c>
+      <c r="U2" s="2">
+        <v>10</v>
+      </c>
+      <c r="V2" s="2">
+        <v>7</v>
+      </c>
+      <c r="W2" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="X2" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>7</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB2" s="2">
+        <v>28</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>14</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AE2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AF2" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="AG2" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="AH2" s="2">
+        <v>28</v>
+      </c>
+      <c r="AI2" s="2">
+        <v>100000000</v>
+      </c>
+      <c r="AJ2" s="2">
+        <v>9</v>
+      </c>
+      <c r="AK2" s="2">
+        <v>10</v>
+      </c>
+      <c r="AL2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="2">
+        <v>10000</v>
+      </c>
+      <c r="AN2" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="AP2" s="2">
+        <v>2</v>
+      </c>
+      <c r="AQ2" s="2">
+        <v>10</v>
+      </c>
+      <c r="AR2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F49480-722F-4F2F-A13A-591DDB093F83}">
+  <sheetPr codeName="Sheet12"/>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" style="2"/>
+    <col min="17" max="17" width="23" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>431</v>
+      </c>
+      <c r="H1" s="18"/>
+      <c r="J1" s="18"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" s="2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B4" s="2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B6" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B7" s="2">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B8" s="2">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B11" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B12" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B19" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B20" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B21" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B22" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B23" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B26" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B28" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B29" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B30" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B35" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B36" s="2">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B37" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B38" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B40" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B41" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B43" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B44" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B45" s="2">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F2FEB3-FC18-488E-84C9-FF47B12E7425}">
+  <sheetPr codeName="Sheet13"/>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="17" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="str" cm="1">
+        <f t="array" ref="A1:A45">_xlfn.TOCOL(ConfigDataTable_Edit!A:A, 1)</f>
+        <v>Column</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="str">
+        <v>UsedBatteryPerWork</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="str">
+        <v>RealTimePerDay</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="str">
+        <v>DaysPerYear</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="str">
+        <v>DaysPerMonth</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="str">
+        <v>RocketSlotAmount</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="str">
+        <v>RocketDeliveryTime</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="str">
+        <v>RocketLoadingTime</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="str">
+        <v>BadEndGraceDays</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="str">
+        <v>GraceInterest</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="str">
+        <v>MarketOpenHour</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="str">
+        <v>MarketCloseHour</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="str">
+        <v>EventProb</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="str">
+        <v>RumorProb</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="str">
+        <v>RumorStdMul</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="str">
+        <v>FollowUpDecay</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="str">
+        <v>FollowUpOverMeanMul</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="str">
+        <v>EmgProb</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="str">
+        <v>EmgMinDays</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="str">
+        <v>EmgMaxDays</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="str">
+        <v>EmgCoolDownDays</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="str">
+        <v>EmgAfterLockReachDays</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="str">
+        <v>EmgAfterLockExpireDays</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="str">
+        <v>EmgLockDecay</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="str">
+        <v>EmgVirtualLineMul</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="str">
+        <v>EmgVirtualLineKeepDays</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="str">
+        <v>RegressionRangeMin</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="str">
+        <v>RegressionRangeMax</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="str">
+        <v>LineSampleDays</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="str">
+        <v>LineSettleDays</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="str">
+        <v>LineBinSigma</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="str">
+        <v>LineMinSamples</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="str">
+        <v>LineBlockDecay</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="str">
+        <v>LineQuietPower</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="str">
+        <v>TaxPeriodDays</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="str">
+        <v>EndingGoalMoney</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="str">
+        <v>StartingPotatoSeed</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="str">
+        <v>StartingPotato</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="str">
+        <v>StartingNPC</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="str">
+        <v>StartingMoney</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="str">
+        <v>ExpireWarningDays</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="str">
+        <v>TimeScaleStep</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="str">
+        <v>TimeScaleMax</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="str">
+        <v>UITimeStepMinutes</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="str">
+        <v>FieldMaxExpand</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448FCFD8-7062-4DFA-B86D-C27384DBCAB4}">
-  <dimension ref="A1:C7"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.875" style="2" bestFit="1" customWidth="1"/>
@@ -6336,47 +8042,47 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="str" cm="1">
-        <f t="array" ref="A2:A7">TRANSPOSE(ItemDataTable!A1:F1)</f>
-        <v>ItemID</v>
+        <f t="array" ref="A2:A8">TRANSPOSE(ItemDataTable!A1:G1)</f>
+        <v>ID</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="str">
-        <v>ItemName</v>
+        <v>Name</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="str">
-        <v>ItemType</v>
+        <v>Type</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -6384,10 +8090,10 @@
         <v>BasicPrice</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -6395,21 +8101,26 @@
         <v>Stack</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="str">
+        <v>MaxCapacity</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="str">
         <v>StoragePeriod</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -6420,416 +8131,1078 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC52DA5-BF28-40FD-BA0C-E037F8F1DE98}">
-  <dimension ref="A1:C33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20862AF-9F9A-48F1-AC3A-75C77964B415}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1012</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <f>VLOOKUP(A2, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Corn</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>VLOOKUP(A2, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1022</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <f>VLOOKUP(A3, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Potato</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f>VLOOKUP(A3, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="2">
+        <v>60</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>1021</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2012</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Carrot</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f>VLOOKUP(A4, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="E4" s="2">
+        <v>120</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>1022</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <f>VLOOKUP(A5, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Onion</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f>VLOOKUP(A5, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3012</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <f>VLOOKUP(A6, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Strawberry</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f>VLOOKUP(A6, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E6" s="2">
+        <v>300</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3022</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <f>VLOOKUP(A7, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>BlueBerry</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f>VLOOKUP(A7, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D7" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>3021</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>3022</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
         <v>4012</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>5001</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>5011</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C17" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>5021</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C18" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>6021</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>6031</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>6032</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>7011</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>8011</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>8012</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>8021</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>8022</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>8031</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>8032</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>8041</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>8042</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>9001</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C31" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>9011</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>9021</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" t="s">
-        <v>397</v>
+      <c r="B8" s="2" t="str">
+        <f>VLOOKUP(A8, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Milk</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f>VLOOKUP(A8, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="expression" dxfId="13" priority="1">
-      <formula>AND($A1 &gt;= 6000, $A1 &lt; 7000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
-      <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="3">
-      <formula>AND($A1 &gt;= 5000, $A1 &lt; 6000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="4">
-      <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="5">
-      <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="6">
-      <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8">
-      <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
+      <formula>OR($C1="Seed",$C1="Material")</formula>
     </cfRule>
   </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1832395-F88D-430F-A64D-C09D9FD6DD70}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A10">TRANSPOSE(ProductDataTable!A1:I1)</f>
+        <v>ID</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <v>PriceStdDev</v>
+      </c>
+      <c r="B5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <v>GrowthTime</v>
+      </c>
+      <c r="B6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <v>MaxYield</v>
+      </c>
+      <c r="B7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <v>MinYield</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="8.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="9" style="3"/>
+    <col min="16" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>6011</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5</v>
+      </c>
+      <c r="E2" s="3">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>10</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>-1</v>
+      </c>
+      <c r="K2" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>6021</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="3">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3">
+        <v>6</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>-1</v>
+      </c>
+      <c r="K3" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>6031</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>6</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3">
+        <v>4011</v>
+      </c>
+      <c r="K4" s="3">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>6032</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>12</v>
+      </c>
+      <c r="J5" s="3">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B4 A5:A1048576">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>Prototype</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A10">TRANSPOSE(ObjectDataTable!A1:I1)</f>
+        <v>ID</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>Name</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <v>MainInv</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <v>SubInv</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <v>Speed</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <v>WorkDuration</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <v>DailyYield</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <v>YieldCoolDown</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B11" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" style="2"/>
+    <col min="5" max="5" width="106.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>102</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-0.01</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>104</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>106</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>201</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>202</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="2">
+        <v>201</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>203</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D10" s="2">
+        <v>202</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>211</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>212</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>213</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>214</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D14" s="2">
+        <v>213</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>301</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>302</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>303</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D17" s="2">
+        <v>302</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>304</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="2">
+        <v>-0.02</v>
+      </c>
+      <c r="D18" s="2">
+        <v>302</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>311</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>312</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
+    <sortCondition ref="A2:A20"/>
+  </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A20">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>AND(A2 &gt; 300, A2 &lt; 400)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>AND(A2 &gt; 200, A2 &lt; 300)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>AND(A2 &gt; 100, A2 &lt; 200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D902D-6443-438F-90C7-179D093475FD}">
-  <dimension ref="A1:H12"/>
+  <sheetPr codeName="Sheet8"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.125" style="2" bestFit="1" customWidth="1"/>
@@ -6842,28 +9215,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>176</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -6871,25 +9244,25 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>163</v>
+        <v>394</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -6897,1398 +9270,780 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>143</v>
+        <v>400</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>142</v>
+        <v>390</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>168</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>145</v>
+        <v>395</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>144</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>169</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>147</v>
+        <v>401</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>146</v>
+        <v>392</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>170</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>149</v>
+        <v>396</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>162</v>
+        <v>394</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>148</v>
+        <v>393</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>171</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>181</v>
+        <v>403</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
+        <v>143</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2</v>
+        <v>143</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D12" s="2">
-        <v>3</v>
+        <v>143</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>175</v>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>41</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>42</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>43</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
-    <sortCondition ref="A2:A13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H16">
+    <sortCondition ref="A2:A16"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20862AF-9F9A-48F1-AC3A-75C77964B415}">
-  <dimension ref="A1:I8"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC52DA5-BF28-40FD-BA0C-E037F8F1DE98}">
+  <sheetPr codeName="Sheet9"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    <row r="1" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>1021</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>1022</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>3011</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>3012</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <f>VLOOKUP(A2, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Corn</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <f>VLOOKUP(A2, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="E2" s="2">
-        <f>VLOOKUP(A2, ItemDataTable!A:D,4, FALSE)</f>
-        <v>1000</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2">
+      <c r="C11" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>3021</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>3022</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>4011</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>4012</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>1022</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <f>VLOOKUP(A3, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Potato</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <f>VLOOKUP(A3, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="E3" s="2">
-        <f>VLOOKUP(A3, ItemDataTable!A:D,4, FALSE)</f>
-        <v>900</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Carrot</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <f>VLOOKUP(A4, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="E4" s="2">
-        <f>VLOOKUP(A4, ItemDataTable!A:D,4, FALSE)</f>
-        <v>1000</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B5" s="2" t="str">
-        <f>VLOOKUP(A5, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Onion</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <f>VLOOKUP(A5, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="E5" s="2">
-        <f>VLOOKUP(A5, ItemDataTable!A:D,4, FALSE)</f>
-        <v>1100</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B6" s="2" t="str">
-        <f>VLOOKUP(A6, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Strawberry</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <f>VLOOKUP(A6, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="E6" s="2">
-        <f>VLOOKUP(A6, ItemDataTable!A:D,4, FALSE)</f>
-        <v>1200</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>3022</v>
-      </c>
-      <c r="B7" s="2" t="str">
-        <f>VLOOKUP(A7, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>BlueBerry</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <f>VLOOKUP(A7, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D7" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E7" s="2">
-        <f>VLOOKUP(A7, ItemDataTable!A:D,4, FALSE)</f>
-        <v>1100</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>4012</v>
-      </c>
-      <c r="B8" s="2" t="str">
-        <f>VLOOKUP(A8, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Milk</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <f>VLOOKUP(A8, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E8" s="2">
-        <f>VLOOKUP(A8, ItemDataTable!A:D,4, FALSE)</f>
-        <v>5000</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="2">
-        <v>5</v>
+      <c r="C15" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>5001</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>5011</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>5021</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>6021</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>6031</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>6032</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>7011</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>8011</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>8012</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>8021</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>8022</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>8031</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>8032</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>8041</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>8042</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>9001</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>9011</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>9021</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>OR($C1="Seed",$C1="Material")</formula>
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>AND($A1 &gt;= 6000, $A1 &lt; 7000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="3">
+      <formula>AND($A1 &gt;= 5000, $A1 &lt; 6000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="6">
+      <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="7">
+      <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="8">
+      <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67515829-0AFB-4F47-8C6E-31EBDF1B0551}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>4012</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Milk</v>
-      </c>
-      <c r="C4" s="2">
-        <f>VLOOKUP(A4-1, ItemDataTable!A:D, 4, FALSE)</f>
-        <v>5000</v>
-      </c>
-      <c r="D4" s="2">
-        <f>VLOOKUP(A4, ProductDataTable!A:E,5, FALSE)</f>
-        <v>5000</v>
-      </c>
-      <c r="E4" s="2">
-        <f>VLOOKUP(A4, ProductDataTable!A:E,4, FALSE)</f>
-        <v>0.2</v>
-      </c>
-      <c r="F4" s="11">
-        <f>D4*(1-(E4*2))</f>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C6" s="2">
-        <f>1000/100*90</f>
-        <v>900</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="F6" s="12">
-        <f>D6*(1-(E6*2))</f>
-        <v>880</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F2"/>
-  </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1832395-F88D-430F-A64D-C09D9FD6DD70}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A10">TRANSPOSE(ProductDataTable!A1:I1)</f>
-        <v>ItemID</v>
-      </c>
-      <c r="B2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <v>ItemName</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="str">
-        <v>ItemType</v>
-      </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="str">
-        <v>PriceStdDev</v>
-      </c>
-      <c r="B5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="str">
-        <v>BasicPrice</v>
-      </c>
-      <c r="B6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <v>GrowthTime</v>
-      </c>
-      <c r="B7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
-        <v>MaxYield</v>
-      </c>
-      <c r="B8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <v>MinYield</v>
-      </c>
-      <c r="B9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <v>WaterConsumption</v>
-      </c>
-      <c r="B10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="2"/>
-    <col min="5" max="5" width="106.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>101</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>102</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>103</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>104</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>105</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>106</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-0.05</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>201</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>202</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D9" s="2">
-        <v>201</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>203</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="D10" s="2">
-        <v>202</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>211</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>212</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2">
-        <v>-0.05</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>213</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>214</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D14" s="2">
-        <v>213</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>301</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>302</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>303</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="D17" s="2">
-        <v>302</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>304</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="2">
-        <v>-0.02</v>
-      </c>
-      <c r="D18" s="2">
-        <v>302</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>311</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>312</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
-    <sortCondition ref="A2:A20"/>
-  </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A20">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>AND(A2 &gt; 300, A2 &lt; 400)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>AND(A2 &gt; 200, A2 &lt; 300)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>AND(A2 &gt; 100, A2 &lt; 200)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>6011</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>2</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>6021</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="3">
-        <v>10000</v>
-      </c>
-      <c r="E3" s="3">
-        <v>10</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3">
-        <v>6</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>6031</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="3">
-        <v>20000</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>6</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>6032</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B4 A5:A1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>Prototype</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -1,35 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751A38E9-33A7-4E82-83A7-282AFA983D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C89DADF-1CE2-4049-B802-725A44940926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" firstSheet="4" activeTab="11" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="2" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
     <sheet name="ItemDataTable_Meta" sheetId="7" r:id="rId2"/>
-    <sheet name="ProductDataTable" sheetId="3" r:id="rId3"/>
-    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId4"/>
-    <sheet name="ObjectDataTable" sheetId="5" r:id="rId5"/>
-    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId6"/>
-    <sheet name="EventDataTable" sheetId="4" r:id="rId7"/>
-    <sheet name="KeycodeDataTable" sheetId="13" r:id="rId8"/>
-    <sheet name="LocalizationTable" sheetId="15" r:id="rId9"/>
-    <sheet name="Calculator" sheetId="14" r:id="rId10"/>
+    <sheet name="LocalizationTable" sheetId="15" r:id="rId3"/>
+    <sheet name="KeycodeDataTable" sheetId="13" r:id="rId4"/>
+    <sheet name="ProductDataTable" sheetId="3" r:id="rId5"/>
+    <sheet name="Calculator" sheetId="14" r:id="rId6"/>
+    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId7"/>
+    <sheet name="EventDataTable" sheetId="4" r:id="rId8"/>
+    <sheet name="ObjectDataTable" sheetId="5" r:id="rId9"/>
+    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId10"/>
     <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId11"/>
-    <sheet name="ConfigDataTable" sheetId="18" r:id="rId12"/>
-    <sheet name="ConfigDataTable_Edit" sheetId="16" r:id="rId13"/>
-    <sheet name="ConfigDataTable_Meta" sheetId="17" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -69,7 +65,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="398">
+  <si>
+    <t>ItemID</t>
+  </si>
+  <si>
+    <t>ItemName</t>
+  </si>
   <si>
     <t>PriceStdDev</t>
   </si>
@@ -77,6 +79,9 @@
     <t>GrowthTime</t>
   </si>
   <si>
+    <t>WaterConsumption</t>
+  </si>
+  <si>
     <t>Potato</t>
   </si>
   <si>
@@ -101,6 +106,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Seed</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -122,6 +131,18 @@
   </si>
   <si>
     <t>StoragePeriod</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EventType</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -332,6 +353,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>BasicPrice</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Type</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -488,10 +513,22 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>ObjectID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Cow</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>ObjectName</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ObjectType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Cattle</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -502,6 +539,10 @@
   <si>
     <t>NPC</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Price</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Chicken</t>
@@ -512,6 +553,10 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
+    <t>ProductionAmount</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>오브젝트 일련번호</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -548,9 +593,17 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>데모버전 사용 여부</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>TargetUI</t>
   </si>
   <si>
+    <t>ActionType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>IsRebindable</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -579,6 +632,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>S</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>PopUp_Shop</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -627,14 +684,26 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>Chicken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Object</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>KeyID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>DefaultKeyCode</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>Movement</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>UI</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -688,6 +757,10 @@
   </si>
   <si>
     <t>3번 슬롯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionName</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -1993,6 +2066,10 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Korean</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -2114,466 +2191,6 @@
   </si>
   <si>
     <t>축사</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>DailyYield</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>YieldCoolDown</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sheep</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>YieldMaterial</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>YieldItem</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxCapacity</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>W</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>S</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Movement</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC_MoveLeft</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC_MoveRight</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>위로 이동</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>왼쪽으로 이동</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아래로 이동</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC_MoveUp</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC_MoveDown</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>오른쪽으로 이동</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>M</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RealTimePerDay</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RocketSlotAmount</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RocketDeliveryTime</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RocketLoadingTime</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>GraceInterest</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>MarketOpenHour</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>MarketCloseHour</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>행동 마다 사용되는 베터리 용량</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 기준 1년</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 기준 1달</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>로켓 용량</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EventProb</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RumorProb</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RumorStdMul</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FollowUpDecay</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FollowUpOverMeanMul</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>유예 기간 이자 비율</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>로켓 이동 시간(초 단위)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>로켓 상하차 시간(초 단위)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 오버 유예 기간(게임 내 일 단위)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>장 마감 시간(게임 내 시간 단위)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>게임 내 하루의 실제 시간(초 단위)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이벤트 발생 확률</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>소문 발생 확률</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>소문 적용 시 표준편차 변동 비율</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>후속 이벤트 발생 확률(0.7^연속 일수)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>목표 미달 시 반전될 확률</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Value</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>긴급 이벤트 발생 확률</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>긴급 이벤트 최소 진행 기간</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>긴급 이벤트 최대 진행 기간</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>긴급 이벤트 재 발생 쿨 타임</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgProb</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgMinDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgMaxDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgAfterLockReachDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgAfterLockExpireDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgLockDecay</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>긴급 이벤트 목표 달성 종료 시,  평균 회귀 유예 최소 기간</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>긴급 이벤트 기간 만료 종료 시, 평균 회귀 유예 최소 기간</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>유예 최소 기간 이후 유예 유지 확률 (0.7 ^ 연속 일수)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>UsedBatteryPerWork</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>DaysPerYear</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>DaysPerMonth</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgVirtualLineMul</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>긴급 이벤트 가상 선 강도 (기존 지지/저항 선의 0.3배)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgVirtualLineKeepDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>가상선 유지 기간</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegressionRangeMin</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>RegressionRangeMax</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LineSampleDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LineSettleDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LineBinSigma</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지지/저항선 표본</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지지/저항선 형성 주기</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LineMinSamples</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>선이 형성되기 위한 최소한의 표본 개수</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LineBlockDecay</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>LineQuietPower</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지지/저항선이 한 번 부딪힐 때 줄어드는 강도 비율</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TaxPeriodDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EndingGoalMoney</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartingPotatoSeed</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartingPotato</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartingNPC</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartingMoney</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>세금 지출 주기</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>굿 엔딩 기준 금액</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>시작 지원 아이템 : 씨 감자</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>시작 지원 아이템 : 감자</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>시작 지원 아이템 : 기본 NPC 로봇</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>시작 지원 아이템 : 정착 지원금</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EmgCoolDownDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>BadEndGraceDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>평균회귀 목표 예외 범위(0.5~2배를 벗어난 경우엔 원가를 목표로)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>28일 표본 중, 비슷한 가격대 끼리 묶는 배수</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>장 시작 시간(게임 내 시간 단위)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이벤트가 없는 날의 고정 돌파 강도</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpireWarningDays</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TimeScaleMax</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TimeScaleStep</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>유통기한 경고 일수</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간 배수 증가 배율 (0.5씩 증가)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 시간 배수 증가 수치</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>UITimeStepMinutes</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>FieldMaxExpand</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI 시간 표시 최소 단위(10분단위)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>각 방향 별 필드 확장 최대 횟수</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2581,9 +2198,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
-  </numFmts>
   <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2798,7 +2412,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3011,18 +2625,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3286,7 +2888,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3334,18 +2936,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3399,6 +2989,41 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="23">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3459,41 +3084,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3890,59 +3480,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6335F4D-6333-4BEC-B869-C3B1C6B3F47D}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="13.125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11.625" style="2" customWidth="1"/>
     <col min="11" max="11" width="11.875" style="2" customWidth="1"/>
     <col min="12" max="12" width="11.5" style="2" customWidth="1"/>
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>389</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1011</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2">
         <f>D3*90/100</f>
@@ -3952,24 +3537,21 @@
         <v>45</v>
       </c>
       <c r="F2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1012</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2">
         <v>1000</v>
@@ -3978,24 +3560,21 @@
         <v>9</v>
       </c>
       <c r="F3" s="2">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="2">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1021</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
         <v>800</v>
@@ -4004,24 +3583,21 @@
         <v>45</v>
       </c>
       <c r="F4" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G4" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
         <v>900</v>
@@ -4030,24 +3606,21 @@
         <v>9</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2011</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2">
         <f>D7*90/100</f>
@@ -4057,24 +3630,21 @@
         <v>45</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G6" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2012</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
         <v>1000</v>
@@ -4083,24 +3653,21 @@
         <v>9</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2">
         <f>D9*90/100</f>
@@ -4110,24 +3677,21 @@
         <v>45</v>
       </c>
       <c r="F8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="2">
         <v>0</v>
       </c>
-      <c r="G8" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2">
         <v>1100</v>
@@ -4136,24 +3700,21 @@
         <v>9</v>
       </c>
       <c r="F9" s="2">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2">
         <v>0</v>
       </c>
-      <c r="G9" s="2">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>3011</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
         <v>1100</v>
@@ -4162,24 +3723,21 @@
         <v>45</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G10" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>3012</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2">
         <v>1200</v>
@@ -4188,24 +3746,21 @@
         <v>9</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G11" s="2">
-        <v>15</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>3021</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2">
         <f>D13*90/100</f>
@@ -4215,24 +3770,21 @@
         <v>45</v>
       </c>
       <c r="F12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="2">
         <v>0</v>
       </c>
-      <c r="G12" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>3022</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2">
         <v>1100</v>
@@ -4241,24 +3793,21 @@
         <v>9</v>
       </c>
       <c r="F13" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2">
         <v>0</v>
       </c>
-      <c r="G13" s="2">
-        <v>15</v>
-      </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>4011</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2">
         <v>5000</v>
@@ -4267,24 +3816,21 @@
         <v>8</v>
       </c>
       <c r="F14" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>4012</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2">
         <v>5000</v>
@@ -4293,24 +3839,21 @@
         <v>4</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G15" s="2">
-        <v>7</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>5001</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -4319,24 +3862,21 @@
         <v>99</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G16" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>5011</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -4345,24 +3885,21 @@
         <v>1</v>
       </c>
       <c r="F17" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G17" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>5021</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -4371,24 +3908,21 @@
         <v>1</v>
       </c>
       <c r="F18" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G18" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>6021</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D19" s="2">
         <v>10000</v>
@@ -4397,24 +3931,21 @@
         <v>1</v>
       </c>
       <c r="F19" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G19" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>6031</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D20" s="2">
         <v>20000</v>
@@ -4423,24 +3954,21 @@
         <v>1</v>
       </c>
       <c r="F20" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G20" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>6032</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>379</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="D21" s="2">
         <v>5000</v>
@@ -4449,24 +3977,21 @@
         <v>1</v>
       </c>
       <c r="F21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G21" s="2">
         <v>0</v>
       </c>
-      <c r="G21" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>7011</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D22" s="2">
         <v>1000</v>
@@ -4475,24 +4000,21 @@
         <v>1</v>
       </c>
       <c r="F22" s="2">
-        <v>300</v>
+        <v>-1</v>
       </c>
       <c r="G22" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H22" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>8011</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D23" s="2">
         <v>10000</v>
@@ -4501,24 +4023,21 @@
         <v>1</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G23" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H23" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>8012</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D24" s="2">
         <v>20000</v>
@@ -4527,24 +4046,21 @@
         <v>1</v>
       </c>
       <c r="F24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G24" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>8021</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D25" s="2">
         <v>10000</v>
@@ -4553,24 +4069,21 @@
         <v>1</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G25" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>8022</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D26" s="2">
         <v>20000</v>
@@ -4579,24 +4092,21 @@
         <v>1</v>
       </c>
       <c r="F26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="2">
         <v>0</v>
       </c>
-      <c r="G26" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>8031</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D27" s="2">
         <v>10000</v>
@@ -4605,24 +4115,21 @@
         <v>1</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G27" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H27" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>8032</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D28" s="2">
         <v>20000</v>
@@ -4631,24 +4138,21 @@
         <v>1</v>
       </c>
       <c r="F28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G28" s="2">
         <v>0</v>
       </c>
-      <c r="G28" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>8041</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2">
         <v>10000</v>
@@ -4657,24 +4161,21 @@
         <v>1</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G29" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>8042</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D30" s="2">
         <v>20000</v>
@@ -4683,24 +4184,21 @@
         <v>1</v>
       </c>
       <c r="F30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G30" s="2">
         <v>0</v>
       </c>
-      <c r="G30" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>9001</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -4709,24 +4207,21 @@
         <v>1</v>
       </c>
       <c r="F31" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G31" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>9011</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D32" s="2">
         <v>100000</v>
@@ -4735,24 +4230,21 @@
         <v>1</v>
       </c>
       <c r="F32" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G32" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H32" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>9021</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D33" s="2">
         <v>30000</v>
@@ -4761,13 +4253,15 @@
         <v>1</v>
       </c>
       <c r="F33" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G33" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H33" s="2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L38" s="2" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -4810,101 +4304,137 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67515829-0AFB-4F47-8C6E-31EBDF1B0551}">
-  <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:F6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>4012</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Milk</v>
-      </c>
-      <c r="C4" s="2">
-        <f>VLOOKUP(A4-1, ItemDataTable!A:D, 4, FALSE)</f>
-        <v>5000</v>
-      </c>
-      <c r="D4" s="2">
-        <f>VLOOKUP(A4, ProductDataTable!A:E,5, FALSE)</f>
-        <v>-1</v>
-      </c>
-      <c r="E4" s="2">
-        <f>VLOOKUP(A4, ProductDataTable!A:E,4, FALSE)</f>
-        <v>0.2</v>
-      </c>
-      <c r="F4" s="11">
-        <f>D4*(1-(E4*2))</f>
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C6" s="2">
-        <f>1000/100*90</f>
-        <v>900</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0.06</v>
-      </c>
-      <c r="F6" s="12">
-        <f>D6*(1-(E6*2))</f>
-        <v>880</v>
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A11">TRANSPOSE(ObjectDataTable!A1:J1)</f>
+        <v>ObjectID</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>ObjectName</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <v>ObjectType</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <v>Price</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <v>MainInv</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <v>SubInv</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <v>Speed</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <v>WorkDuration</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <v>ProductionAmount</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <v>UseToDemo</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F2"/>
-  </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4912,7 +4442,6 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
-  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:F110"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4927,22 +4456,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -4950,13 +4479,13 @@
         <v>100001</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
@@ -4966,13 +4495,13 @@
         <v>100002</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -4982,13 +4511,13 @@
         <v>100003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4998,13 +4527,13 @@
         <v>110001</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -5014,17 +4543,17 @@
         <v>110002</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="7" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5032,13 +4561,13 @@
         <v>110003</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -5048,13 +4577,13 @@
         <v>110004</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -5064,13 +4593,13 @@
         <v>110005</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -5080,13 +4609,13 @@
         <v>110006</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
@@ -5096,13 +4625,13 @@
         <v>110007</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
@@ -5112,17 +4641,17 @@
         <v>110008</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="7" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5130,13 +4659,13 @@
         <v>110009</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -5146,13 +4675,13 @@
         <v>110010</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -5162,17 +4691,17 @@
         <v>110011</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="7" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5180,13 +4709,13 @@
         <v>110012</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -5196,13 +4725,13 @@
         <v>110013</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -5212,13 +4741,13 @@
         <v>110014</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -5228,17 +4757,17 @@
         <v>110015</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="7" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5246,17 +4775,17 @@
         <v>110016</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="7" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5264,17 +4793,17 @@
         <v>110017</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="7" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5282,13 +4811,13 @@
         <v>110018</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -5298,13 +4827,13 @@
         <v>110019</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -5314,17 +4843,17 @@
         <v>110020</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="7" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5332,13 +4861,13 @@
         <v>110021</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -5348,13 +4877,13 @@
         <v>110022</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -5364,17 +4893,17 @@
         <v>110023</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="7" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5382,17 +4911,17 @@
         <v>110024</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="7" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5400,13 +4929,13 @@
         <v>110025</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -5416,13 +4945,13 @@
         <v>110026</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -5432,13 +4961,13 @@
         <v>110027</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -5448,17 +4977,17 @@
         <v>110028</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="7" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5466,17 +4995,17 @@
         <v>110029</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="7" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5484,17 +5013,17 @@
         <v>110030</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="7" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5502,17 +5031,17 @@
         <v>110031</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="E35" s="8"/>
       <c r="F35" s="7" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5520,17 +5049,17 @@
         <v>110032</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="E36" s="8"/>
       <c r="F36" s="7" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5538,13 +5067,13 @@
         <v>110033</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="E37" s="8"/>
       <c r="F37" s="7"/>
@@ -5554,13 +5083,13 @@
         <v>110034</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="8"/>
@@ -5570,13 +5099,13 @@
         <v>110035</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
@@ -5586,13 +5115,13 @@
         <v>110036</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
@@ -5602,13 +5131,13 @@
         <v>110037</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
@@ -5618,17 +5147,17 @@
         <v>110038</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="7" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5636,17 +5165,17 @@
         <v>110039</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="E43" s="8"/>
       <c r="F43" s="7" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5654,13 +5183,13 @@
         <v>110040</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -5670,17 +5199,17 @@
         <v>110041</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="E45" s="8"/>
       <c r="F45" s="7" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5688,13 +5217,13 @@
         <v>110042</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
@@ -5704,17 +5233,17 @@
         <v>110043</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="E47" s="8"/>
       <c r="F47" s="7" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5722,17 +5251,17 @@
         <v>110044</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="E48" s="8"/>
       <c r="F48" s="7" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5740,17 +5269,17 @@
         <v>110045</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="E49" s="8"/>
       <c r="F49" s="7" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5758,13 +5287,13 @@
         <v>110046</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
@@ -5774,17 +5303,17 @@
         <v>110047</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="7" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5792,13 +5321,13 @@
         <v>110048</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
@@ -5808,17 +5337,17 @@
         <v>110049</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="7" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5826,17 +5355,17 @@
         <v>110050</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="7" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5844,13 +5373,13 @@
         <v>110051</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
@@ -5860,17 +5389,17 @@
         <v>110052</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="7" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5878,13 +5407,13 @@
         <v>110053</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -5894,13 +5423,13 @@
         <v>110054</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
@@ -5910,13 +5439,13 @@
         <v>110055</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
@@ -5926,13 +5455,13 @@
         <v>110056</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
@@ -5942,17 +5471,17 @@
         <v>110057</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="7" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -5960,13 +5489,13 @@
         <v>110058</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
@@ -5976,13 +5505,13 @@
         <v>110059</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
@@ -5992,13 +5521,13 @@
         <v>110060</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
@@ -6008,17 +5537,17 @@
         <v>110061</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="7" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6026,13 +5555,13 @@
         <v>110062</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
@@ -6042,13 +5571,13 @@
         <v>110063</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
@@ -6058,17 +5587,17 @@
         <v>110064</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="7" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6076,17 +5605,17 @@
         <v>110065</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="7" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6094,17 +5623,17 @@
         <v>110066</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="7" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6112,17 +5641,17 @@
         <v>110067</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="E71" s="8"/>
       <c r="F71" s="7" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6130,17 +5659,17 @@
         <v>110068</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="E72" s="8"/>
       <c r="F72" s="7" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6148,17 +5677,17 @@
         <v>110069</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="E73" s="8"/>
       <c r="F73" s="7" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6166,13 +5695,13 @@
         <v>110070</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="E74" s="8"/>
       <c r="F74" s="8"/>
@@ -6182,17 +5711,17 @@
         <v>110071</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="E75" s="8"/>
       <c r="F75" s="7" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6200,13 +5729,13 @@
         <v>110072</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
@@ -6216,13 +5745,13 @@
         <v>110073</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
@@ -6232,13 +5761,13 @@
         <v>110074</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
@@ -6248,13 +5777,13 @@
         <v>110075</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
@@ -6264,17 +5793,17 @@
         <v>110076</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="E80" s="8"/>
       <c r="F80" s="7" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6282,13 +5811,13 @@
         <v>110077</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
@@ -6298,13 +5827,13 @@
         <v>110078</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
@@ -6314,17 +5843,17 @@
         <v>110079</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="E83" s="8"/>
       <c r="F83" s="7" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6332,17 +5861,17 @@
         <v>110080</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="E84" s="8"/>
       <c r="F84" s="7" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6350,13 +5879,13 @@
         <v>110081</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
@@ -6366,17 +5895,17 @@
         <v>110082</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="E86" s="8"/>
       <c r="F86" s="7" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6384,13 +5913,13 @@
         <v>110083</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
@@ -6400,17 +5929,17 @@
         <v>110084</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="E88" s="8"/>
       <c r="F88" s="9" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6418,13 +5947,13 @@
         <v>110085</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
@@ -6434,13 +5963,13 @@
         <v>110086</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
@@ -6450,13 +5979,13 @@
         <v>110087</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
@@ -6466,13 +5995,13 @@
         <v>110088</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
@@ -6482,17 +6011,17 @@
         <v>110089</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="E93" s="8"/>
       <c r="F93" s="7" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6500,17 +6029,17 @@
         <v>110090</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="E94" s="8"/>
       <c r="F94" s="7" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6518,13 +6047,13 @@
         <v>110091</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
@@ -6534,13 +6063,13 @@
         <v>110092</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
@@ -6550,17 +6079,17 @@
         <v>110093</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="E97" s="8"/>
       <c r="F97" s="7" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6568,17 +6097,17 @@
         <v>110094</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="E98" s="8"/>
       <c r="F98" s="7" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6586,17 +6115,17 @@
         <v>110095</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="E99" s="8"/>
       <c r="F99" s="7" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6604,13 +6133,13 @@
         <v>110096</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
@@ -6620,13 +6149,13 @@
         <v>110097</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
@@ -6636,17 +6165,17 @@
         <v>110098</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="E102" s="8"/>
       <c r="F102" s="7" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6654,13 +6183,13 @@
         <v>110099</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
@@ -6670,13 +6199,13 @@
         <v>110100</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
@@ -6686,17 +6215,17 @@
         <v>110101</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="E105" s="8"/>
       <c r="F105" s="7" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6704,13 +6233,13 @@
         <v>110102</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
@@ -6720,13 +6249,13 @@
         <v>190001</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="E107" s="8"/>
       <c r="F107" s="8"/>
@@ -6736,17 +6265,17 @@
         <v>190002</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="E108" s="8"/>
       <c r="F108" s="7" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
@@ -6754,13 +6283,13 @@
         <v>190101</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
@@ -6770,13 +6299,13 @@
         <v>190102</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="E110" s="8"/>
       <c r="F110" s="8"/>
@@ -6791,1244 +6320,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F807C416-FB0B-451D-B155-C2F36043718F}">
-  <dimension ref="A1:AR2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="19.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="23.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="20.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="18.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="45" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="str" cm="1">
-        <f t="array" ref="A1:AR2">TRANSPOSE(_xlfn.DROP(_xlfn._xlws.FILTER(ConfigDataTable_Edit!A:B, ConfigDataTable_Edit!A:A&lt;&gt;""), 1))</f>
-        <v>UsedBatteryPerWork</v>
-      </c>
-      <c r="B1" s="2" t="str">
-        <v>RealTimePerDay</v>
-      </c>
-      <c r="C1" s="2" t="str">
-        <v>DaysPerYear</v>
-      </c>
-      <c r="D1" s="2" t="str">
-        <v>DaysPerMonth</v>
-      </c>
-      <c r="E1" s="2" t="str">
-        <v>RocketSlotAmount</v>
-      </c>
-      <c r="F1" s="2" t="str">
-        <v>RocketDeliveryTime</v>
-      </c>
-      <c r="G1" s="2" t="str">
-        <v>RocketLoadingTime</v>
-      </c>
-      <c r="H1" s="2" t="str">
-        <v>BadEndGraceDays</v>
-      </c>
-      <c r="I1" s="2" t="str">
-        <v>GraceInterest</v>
-      </c>
-      <c r="J1" s="2" t="str">
-        <v>MarketOpenHour</v>
-      </c>
-      <c r="K1" s="2" t="str">
-        <v>MarketCloseHour</v>
-      </c>
-      <c r="L1" s="2" t="str">
-        <v>EventProb</v>
-      </c>
-      <c r="M1" s="2" t="str">
-        <v>RumorProb</v>
-      </c>
-      <c r="N1" s="2" t="str">
-        <v>RumorStdMul</v>
-      </c>
-      <c r="O1" s="2" t="str">
-        <v>FollowUpDecay</v>
-      </c>
-      <c r="P1" s="2" t="str">
-        <v>FollowUpOverMeanMul</v>
-      </c>
-      <c r="Q1" s="2" t="str">
-        <v>EmgProb</v>
-      </c>
-      <c r="R1" s="2" t="str">
-        <v>EmgMinDays</v>
-      </c>
-      <c r="S1" s="2" t="str">
-        <v>EmgMaxDays</v>
-      </c>
-      <c r="T1" s="2" t="str">
-        <v>EmgCoolDownDays</v>
-      </c>
-      <c r="U1" s="2" t="str">
-        <v>EmgAfterLockReachDays</v>
-      </c>
-      <c r="V1" s="2" t="str">
-        <v>EmgAfterLockExpireDays</v>
-      </c>
-      <c r="W1" s="2" t="str">
-        <v>EmgLockDecay</v>
-      </c>
-      <c r="X1" s="2" t="str">
-        <v>EmgVirtualLineMul</v>
-      </c>
-      <c r="Y1" s="2" t="str">
-        <v>EmgVirtualLineKeepDays</v>
-      </c>
-      <c r="Z1" s="2" t="str">
-        <v>RegressionRangeMin</v>
-      </c>
-      <c r="AA1" s="2" t="str">
-        <v>RegressionRangeMax</v>
-      </c>
-      <c r="AB1" s="2" t="str">
-        <v>LineSampleDays</v>
-      </c>
-      <c r="AC1" s="2" t="str">
-        <v>LineSettleDays</v>
-      </c>
-      <c r="AD1" s="2" t="str">
-        <v>LineBinSigma</v>
-      </c>
-      <c r="AE1" s="2" t="str">
-        <v>LineMinSamples</v>
-      </c>
-      <c r="AF1" s="2" t="str">
-        <v>LineBlockDecay</v>
-      </c>
-      <c r="AG1" s="2" t="str">
-        <v>LineQuietPower</v>
-      </c>
-      <c r="AH1" s="2" t="str">
-        <v>TaxPeriodDays</v>
-      </c>
-      <c r="AI1" s="2" t="str">
-        <v>EndingGoalMoney</v>
-      </c>
-      <c r="AJ1" s="2" t="str">
-        <v>StartingPotatoSeed</v>
-      </c>
-      <c r="AK1" s="2" t="str">
-        <v>StartingPotato</v>
-      </c>
-      <c r="AL1" s="2" t="str">
-        <v>StartingNPC</v>
-      </c>
-      <c r="AM1" s="2" t="str">
-        <v>StartingMoney</v>
-      </c>
-      <c r="AN1" s="2" t="str">
-        <v>ExpireWarningDays</v>
-      </c>
-      <c r="AO1" s="2" t="str">
-        <v>TimeScaleStep</v>
-      </c>
-      <c r="AP1" s="2" t="str">
-        <v>TimeScaleMax</v>
-      </c>
-      <c r="AQ1" s="2" t="str">
-        <v>UITimeStepMinutes</v>
-      </c>
-      <c r="AR1" s="2" t="str">
-        <v>FieldMaxExpand</v>
-      </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>600</v>
-      </c>
-      <c r="C2" s="2">
-        <v>336</v>
-      </c>
-      <c r="D2" s="2">
-        <v>28</v>
-      </c>
-      <c r="E2" s="2">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2">
-        <v>7200</v>
-      </c>
-      <c r="G2" s="2">
-        <v>7200</v>
-      </c>
-      <c r="H2" s="2">
-        <v>7</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J2" s="2">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2">
-        <v>23</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="N2" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="P2" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="R2" s="2">
-        <v>7</v>
-      </c>
-      <c r="S2" s="2">
-        <v>14</v>
-      </c>
-      <c r="T2" s="2">
-        <v>28</v>
-      </c>
-      <c r="U2" s="2">
-        <v>10</v>
-      </c>
-      <c r="V2" s="2">
-        <v>7</v>
-      </c>
-      <c r="W2" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="X2" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>7</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>2</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>28</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>14</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>2</v>
-      </c>
-      <c r="AF2" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="AG2" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="AH2" s="2">
-        <v>28</v>
-      </c>
-      <c r="AI2" s="2">
-        <v>100000000</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>9</v>
-      </c>
-      <c r="AK2" s="2">
-        <v>10</v>
-      </c>
-      <c r="AL2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM2" s="2">
-        <v>10000</v>
-      </c>
-      <c r="AN2" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="AP2" s="2">
-        <v>2</v>
-      </c>
-      <c r="AQ2" s="2">
-        <v>10</v>
-      </c>
-      <c r="AR2" s="2">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90F49480-722F-4F2F-A13A-591DDB093F83}">
-  <sheetPr codeName="Sheet12"/>
-  <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="2"/>
-    <col min="17" max="17" width="23" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="H1" s="18"/>
-      <c r="J1" s="18"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="B3" s="2">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B4" s="2">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="B5" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B6" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B7" s="2">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="B8" s="2">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="B9" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="B11" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B12" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B15" s="2">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B17" s="2">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B18" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="B19" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="B20" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="B21" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="B22" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="B23" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B24" s="2">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B25" s="2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B26" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="B27" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="B28" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="B29" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="B30" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B31" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B32" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="B33" s="2">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B34" s="2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="B35" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="B36" s="2">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="B37" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="B38" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="B39" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="B40" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B41" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="B42" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B43" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B44" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="B45" s="2">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F2FEB3-FC18-488E-84C9-FF47B12E7425}">
-  <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="17" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="str" cm="1">
-        <f t="array" ref="A1:A45">_xlfn.TOCOL(ConfigDataTable_Edit!A:A, 1)</f>
-        <v>Column</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="str">
-        <v>UsedBatteryPerWork</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="str">
-        <v>RealTimePerDay</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="str">
-        <v>DaysPerYear</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="str">
-        <v>DaysPerMonth</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="str">
-        <v>RocketSlotAmount</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="str">
-        <v>RocketDeliveryTime</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="str">
-        <v>RocketLoadingTime</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="str">
-        <v>BadEndGraceDays</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="str">
-        <v>GraceInterest</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="str">
-        <v>MarketOpenHour</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="str">
-        <v>MarketCloseHour</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="str">
-        <v>EventProb</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="str">
-        <v>RumorProb</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="str">
-        <v>RumorStdMul</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="str">
-        <v>FollowUpDecay</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="str">
-        <v>FollowUpOverMeanMul</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="str">
-        <v>EmgProb</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="str">
-        <v>EmgMinDays</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="str">
-        <v>EmgMaxDays</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="str">
-        <v>EmgCoolDownDays</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="str">
-        <v>EmgAfterLockReachDays</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="str">
-        <v>EmgAfterLockExpireDays</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="str">
-        <v>EmgLockDecay</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="str">
-        <v>EmgVirtualLineMul</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="str">
-        <v>EmgVirtualLineKeepDays</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="str">
-        <v>RegressionRangeMin</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="str">
-        <v>RegressionRangeMax</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="str">
-        <v>LineSampleDays</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="str">
-        <v>LineSettleDays</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="str">
-        <v>LineBinSigma</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="str">
-        <v>LineMinSamples</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="str">
-        <v>LineBlockDecay</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="str">
-        <v>LineQuietPower</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="str">
-        <v>TaxPeriodDays</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="str">
-        <v>EndingGoalMoney</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="str">
-        <v>StartingPotatoSeed</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="str">
-        <v>StartingPotato</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="str">
-        <v>StartingNPC</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="str">
-        <v>StartingMoney</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="str">
-        <v>ExpireWarningDays</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="str">
-        <v>TimeScaleStep</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="str">
-        <v>TimeScaleMax</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="str">
-        <v>UITimeStepMinutes</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="str">
-        <v>FieldMaxExpand</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448FCFD8-7062-4DFA-B86D-C27384DBCAB4}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.875" style="2" bestFit="1" customWidth="1"/>
@@ -8042,47 +6336,47 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="str" cm="1">
-        <f t="array" ref="A2:A8">TRANSPOSE(ItemDataTable!A1:G1)</f>
-        <v>ID</v>
+        <f t="array" ref="A2:A7">TRANSPOSE(ItemDataTable!A1:F1)</f>
+        <v>ItemID</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="str">
-        <v>Name</v>
+        <v>ItemName</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="str">
-        <v>Type</v>
+        <v>ItemType</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -8090,10 +6384,10 @@
         <v>BasicPrice</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -8101,26 +6395,21 @@
         <v>Stack</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="str">
-        <v>MaxCapacity</v>
+        <v>StoragePeriod</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="str">
-        <v>StoragePeriod</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -8131,1078 +6420,416 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20862AF-9F9A-48F1-AC3A-75C77964B415}">
-  <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC52DA5-BF28-40FD-BA0C-E037F8F1DE98}">
+  <dimension ref="A1:C33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>1021</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>1022</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>3011</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>3012</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>3021</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>3022</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>4011</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>4012</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>5001</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>5011</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C17" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>5021</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C18" t="s">
         <v>384</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>6021</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>6031</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>6032</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" t="s">
         <v>385</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>7011</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>8011</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>8012</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>8021</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>8022</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>8031</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>8032</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>8041</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>8042</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <f>VLOOKUP(A2, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Corn</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <f>VLOOKUP(A2, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>1022</v>
-      </c>
-      <c r="B3" s="2" t="str">
-        <f>VLOOKUP(A3, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Potato</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <f>VLOOKUP(A3, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="E3" s="2">
-        <v>60</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B4" s="2" t="str">
-        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Carrot</v>
-      </c>
-      <c r="C4" s="2" t="str">
-        <f>VLOOKUP(A4, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="E4" s="2">
-        <v>120</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B5" s="2" t="str">
-        <f>VLOOKUP(A5, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Onion</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <f>VLOOKUP(A5, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B6" s="2" t="str">
-        <f>VLOOKUP(A6, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Strawberry</v>
-      </c>
-      <c r="C6" s="2" t="str">
-        <f>VLOOKUP(A6, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.08</v>
-      </c>
-      <c r="E6" s="2">
-        <v>300</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>3022</v>
-      </c>
-      <c r="B7" s="2" t="str">
-        <f>VLOOKUP(A7, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>BlueBerry</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <f>VLOOKUP(A7, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D7" s="2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>4012</v>
-      </c>
-      <c r="B8" s="2" t="str">
-        <f>VLOOKUP(A8, ItemDataTable!A:B, 2, FALSE)</f>
-        <v>Milk</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <f>VLOOKUP(A8, ItemDataTable!A:C,3,FALSE)</f>
-        <v>Product</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E8" s="2">
-        <v>-1</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
+      <c r="C30" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>9001</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C31" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>9011</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>9021</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="expression" dxfId="13" priority="1">
-      <formula>OR($C1="Seed",$C1="Material")</formula>
+      <formula>AND($A1 &gt;= 6000, $A1 &lt; 7000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="2">
+      <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>AND($A1 &gt;= 5000, $A1 &lt; 6000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="4">
+      <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="5">
+      <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="6">
+      <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="7">
+      <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="8">
+      <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1832395-F88D-430F-A64D-C09D9FD6DD70}">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A10">TRANSPOSE(ProductDataTable!A1:I1)</f>
-        <v>ID</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="str">
-        <v>Type</v>
-      </c>
-      <c r="B4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="str">
-        <v>PriceStdDev</v>
-      </c>
-      <c r="B5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="str">
-        <v>GrowthTime</v>
-      </c>
-      <c r="B6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <v>MaxYield</v>
-      </c>
-      <c r="B7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
-        <v>MinYield</v>
-      </c>
-      <c r="B8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="8.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9" style="3"/>
-    <col min="16" max="16384" width="9" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>6011</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="3">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K2" s="3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>6021</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="3">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>4</v>
-      </c>
-      <c r="G3" s="3">
-        <v>6</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K3" s="3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>6031</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>6</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>2</v>
-      </c>
-      <c r="I4" s="3">
-        <v>6</v>
-      </c>
-      <c r="J4" s="3">
-        <v>4011</v>
-      </c>
-      <c r="K4" s="3">
-        <v>4012</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>6032</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>3</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3">
-        <v>-1</v>
-      </c>
-      <c r="K5" s="3">
-        <v>-1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B4 A5:A1048576">
-    <cfRule type="expression" dxfId="12" priority="1">
-      <formula>Prototype</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
-  <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A10">TRANSPOSE(ObjectDataTable!A1:I1)</f>
-        <v>ID</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="str">
-        <v>Type</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="str">
-        <v>MainInv</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="str">
-        <v>SubInv</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <v>Speed</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
-        <v>WorkDuration</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <v>DailyYield</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <v>YieldCoolDown</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
-  <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9" style="2"/>
-    <col min="5" max="5" width="106.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>101</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>102</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>103</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>104</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>105</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>106</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-0.05</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>201</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>202</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="D9" s="2">
-        <v>201</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>203</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.02</v>
-      </c>
-      <c r="D10" s="2">
-        <v>202</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>211</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0.05</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>212</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2">
-        <v>-0.05</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>213</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>214</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D14" s="2">
-        <v>213</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>301</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0.03</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>302</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>303</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="D17" s="2">
-        <v>302</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>304</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="2">
-        <v>-0.02</v>
-      </c>
-      <c r="D18" s="2">
-        <v>302</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>311</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0.04</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>312</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
-    <sortCondition ref="A2:A20"/>
-  </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A20">
-    <cfRule type="expression" dxfId="11" priority="1">
-      <formula>AND(A2 &gt; 300, A2 &lt; 400)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
-      <formula>AND(A2 &gt; 200, A2 &lt; 300)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
-      <formula>AND(A2 &gt; 100, A2 &lt; 200)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D902D-6443-438F-90C7-179D093475FD}">
-  <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.125" style="2" bestFit="1" customWidth="1"/>
@@ -9215,28 +6842,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -9244,25 +6871,25 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>394</v>
+        <v>163</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -9270,780 +6897,1398 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>400</v>
+        <v>143</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>394</v>
+        <v>162</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>390</v>
+        <v>142</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>397</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>395</v>
+        <v>145</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>394</v>
+        <v>162</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>391</v>
+        <v>144</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>398</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>401</v>
+        <v>147</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>394</v>
+        <v>162</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>392</v>
+        <v>146</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>399</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>396</v>
+        <v>149</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>394</v>
+        <v>162</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>393</v>
+        <v>148</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>402</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>403</v>
+        <v>181</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>130</v>
+        <v>164</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>134</v>
+        <v>164</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>29</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>41</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>42</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>43</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" s="2">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H16">
-    <sortCondition ref="A2:A16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
+    <sortCondition ref="A2:A13"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC52DA5-BF28-40FD-BA0C-E037F8F1DE98}">
-  <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:C33"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20862AF-9F9A-48F1-AC3A-75C77964B415}">
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="2"/>
+    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="16" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>381</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1011</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1012</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <f>VLOOKUP(A2, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Corn</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>VLOOKUP(A2, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="E2" s="2">
+        <f>VLOOKUP(A2, ItemDataTable!A:D,4, FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1022</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <f>VLOOKUP(A3, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Potato</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f>VLOOKUP(A3, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="2">
+        <f>VLOOKUP(A3, ItemDataTable!A:D,4, FALSE)</f>
+        <v>900</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>1021</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2012</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Carrot</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f>VLOOKUP(A4, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="E4" s="2">
+        <f>VLOOKUP(A4, ItemDataTable!A:D,4, FALSE)</f>
+        <v>1000</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>1022</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <f>VLOOKUP(A5, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Onion</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f>VLOOKUP(A5, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="2">
+        <f>VLOOKUP(A5, ItemDataTable!A:D,4, FALSE)</f>
+        <v>1100</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3012</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <f>VLOOKUP(A6, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Strawberry</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f>VLOOKUP(A6, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E6" s="2">
+        <f>VLOOKUP(A6, ItemDataTable!A:D,4, FALSE)</f>
+        <v>1200</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>3022</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <f>VLOOKUP(A7, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>BlueBerry</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f>VLOOKUP(A7, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D7" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E7" s="2">
+        <f>VLOOKUP(A7, ItemDataTable!A:D,4, FALSE)</f>
+        <v>1100</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>3021</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>3022</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
         <v>4012</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B8" s="2" t="str">
+        <f>VLOOKUP(A8, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Milk</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <f>VLOOKUP(A8, ItemDataTable!A:C,3,FALSE)</f>
+        <v>Product</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="2">
+        <f>VLOOKUP(A8, ItemDataTable!A:D,4, FALSE)</f>
+        <v>5000</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>5</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>5001</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>5011</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>5021</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>6021</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>6031</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>6032</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>7011</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>8011</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>8012</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>8021</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>8022</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>8031</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>8032</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>8041</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>8042</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>9001</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>9011</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>9021</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>AND($A1 &gt;= 6000, $A1 &lt; 7000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>AND($A1 &gt;= 5000, $A1 &lt; 6000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
-      <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="8">
-      <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="9">
-      <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>OR($C1="Seed",$C1="Material")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67515829-0AFB-4F47-8C6E-31EBDF1B0551}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>4012</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Milk</v>
+      </c>
+      <c r="C4" s="2">
+        <f>VLOOKUP(A4-1, ItemDataTable!A:D, 4, FALSE)</f>
+        <v>5000</v>
+      </c>
+      <c r="D4" s="2">
+        <f>VLOOKUP(A4, ProductDataTable!A:E,5, FALSE)</f>
+        <v>5000</v>
+      </c>
+      <c r="E4" s="2">
+        <f>VLOOKUP(A4, ProductDataTable!A:E,4, FALSE)</f>
+        <v>0.2</v>
+      </c>
+      <c r="F4" s="11">
+        <f>D4*(1-(E4*2))</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="2">
+        <f>1000/100*90</f>
+        <v>900</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="F6" s="12">
+        <f>D6*(1-(E6*2))</f>
+        <v>880</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F2"/>
+  </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1832395-F88D-430F-A64D-C09D9FD6DD70}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A10">TRANSPOSE(ProductDataTable!A1:I1)</f>
+        <v>ItemID</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>ItemName</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <v>ItemType</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <v>PriceStdDev</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <v>BasicPrice</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <v>GrowthTime</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <v>MaxYield</v>
+      </c>
+      <c r="B8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <v>MinYield</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <v>WaterConsumption</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" style="2"/>
+    <col min="5" max="5" width="106.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>102</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>-0.01</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>104</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>106</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>201</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>202</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="2">
+        <v>201</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>203</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="D10" s="2">
+        <v>202</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>211</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>212</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <v>-0.05</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>213</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>214</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D14" s="2">
+        <v>213</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>301</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>302</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>303</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D17" s="2">
+        <v>302</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>304</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="2">
+        <v>-0.02</v>
+      </c>
+      <c r="D18" s="2">
+        <v>302</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>311</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>312</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="2">
+        <v>-0.03</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E20">
+    <sortCondition ref="A2:A20"/>
+  </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A20">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>AND(A2 &gt; 300, A2 &lt; 400)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>AND(A2 &gt; 200, A2 &lt; 300)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>AND(A2 &gt; 100, A2 &lt; 200)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>6011</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>2</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>6021</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E3" s="3">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>6031</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>6</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>6032</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>3</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B4 A5:A1048576">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>Prototype</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>